--- a/XBRL-template-MFRS/06-SOCI-NetOfTax.xlsx
+++ b/XBRL-template-MFRS/06-SOCI-NetOfTax.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -67,8 +67,17 @@
       <family val="0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +100,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +142,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -183,6 +197,15 @@
     </xf>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -445,18 +468,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="10">
       <c r="A3" s="12" t="inlineStr">
         <is>
@@ -470,8 +492,8 @@
           <t>Comprehensive income net of tax [abstract]</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="10">
       <c r="A5" s="13" t="inlineStr">
@@ -479,8 +501,8 @@
           <t>Statement of comprehensive income net of tax [line items]</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="10">
       <c r="A6" s="13" t="inlineStr">
@@ -488,8 +510,8 @@
           <t>Statement of comprehensive income [abstract]</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">
       <c r="A7" s="15" t="inlineStr">
@@ -506,8 +528,8 @@
           <t>Other comprehensive income [abstract]</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
     </row>
     <row r="9" ht="23.85" customHeight="1" s="10">
       <c r="A9" s="13" t="inlineStr">
@@ -515,8 +537,8 @@
           <t>Components of other comprehensive income that will not be reclassified to profit or loss, net of tax [abstract]</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
     </row>
     <row r="10" ht="35.05" customHeight="1" s="10">
       <c r="A10" s="15" t="inlineStr">
@@ -584,8 +606,8 @@
           <t>Components of other comprehensive income that will be reclassified to profit or loss, net of tax [abstract]</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="10">
       <c r="A17" s="13" t="inlineStr">
@@ -593,8 +615,8 @@
           <t>Cash flow hedges [abstract]</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="10">
       <c r="A18" s="15" t="inlineStr">
@@ -635,8 +657,8 @@
           <t>Hedges of net investment in foreign operations [abstract]</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
     </row>
     <row r="22" ht="23.85" customHeight="1" s="10">
       <c r="A22" s="15" t="inlineStr">
@@ -677,8 +699,8 @@
           <t>Exchange differences on translation [abstract]</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
     </row>
     <row r="26" ht="23.85" customHeight="1" s="10">
       <c r="A26" s="15" t="inlineStr">
@@ -713,8 +735,8 @@
           <t>Financial assets measured at fair value through other comprehensive income [abstract]</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="14" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
     </row>
     <row r="30" ht="23.85" customHeight="1" s="10">
       <c r="A30" s="15" t="inlineStr">
@@ -827,8 +849,8 @@
           <t>Comprehensive income attributable to [abstract]</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="14" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="10">
       <c r="A40" s="17" t="inlineStr">

--- a/XBRL-template-MFRS/06-SOCI-NetOfTax.xlsx
+++ b/XBRL-template-MFRS/06-SOCI-NetOfTax.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+  </numFmts>
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -76,8 +78,48 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -107,8 +149,26 @@
         <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F8"/>
+        <bgColor rgb="00EEF2F8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -131,6 +191,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -142,7 +221,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -206,6 +285,42 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -460,430 +575,477 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55" customWidth="1" style="9" min="1" max="1"/>
-    <col width="22" customWidth="1" style="9" min="2" max="3"/>
+    <col width="18" customWidth="1" style="9" min="2" max="3"/>
+    <col width="18" customWidth="1" style="10" min="3" max="3"/>
+    <col width="40" customWidth="1" style="10" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="10">
-      <c r="B1" s="21" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="10">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="10">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" s="10">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Statement of comprehensive income, net of tax</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="10">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="D3" s="23" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="10">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Comprehensive income net of tax [abstract]</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="10">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="31" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="10">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Statement of comprehensive income net of tax [line items]</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="10">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="31" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="10">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Statement of comprehensive income [abstract]</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="10">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="10">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Profit (loss)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="10">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="10">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Other comprehensive income [abstract]</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-    </row>
-    <row r="9" ht="23.85" customHeight="1" s="10">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="10">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Components of other comprehensive income that will not be reclassified to profit or loss, net of tax [abstract]</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="20" t="n"/>
-    </row>
-    <row r="10" ht="35.05" customHeight="1" s="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="31" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="10">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Other comprehensive income, net of tax, gains (losses) on revaluation of property, plant and equipment, right-of-use assets and intangible assets</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-    </row>
-    <row r="11" ht="23.85" customHeight="1" s="10">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="32" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="10">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Total other comprehensive income, net of tax, gains (losses) on remeasurements of defined benefit plans</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-    </row>
-    <row r="12" ht="23.85" customHeight="1" s="10">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="33" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="10">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Other comprehensive income, net of tax, gains (losses) from investments in equity instruments</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="23.85" customHeight="1" s="10">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="32" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="10">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Other comprehensive income, net of tax, gains (losses) on other items</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="35.05" customHeight="1" s="10">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="32" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="10">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Share of other comprehensive income of associates and joint ventures accounted for using equity method that will not be reclassified to profit or loss, net of tax</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="10">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="32" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="10">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Total other comprehensive income that will not be reclassified to profit or loss, net of tax</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="29">
         <f>1*B12+1*B13+1*B14</f>
         <v/>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="29">
         <f>1*C12+1*C13+1*C14</f>
         <v/>
       </c>
-    </row>
-    <row r="16" ht="23.85" customHeight="1" s="10">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="D15" s="33" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="10">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Components of other comprehensive income that will be reclassified to profit or loss, net of tax [abstract]</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="10">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="10">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Cash flow hedges [abstract]</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="10">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="10">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Gains (losses) on cash flow hedges, net of tax</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="10">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="32" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="10">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Reclassification adjustments on cash flow hedges, net of tax</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="10">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="32" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="10">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Other comprehensive income, net of tax, cash flow hedges</t>
         </is>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="29">
         <f>1*B18+1*B19</f>
         <v/>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="29">
         <f>1*C18+1*C19</f>
         <v/>
       </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="10">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="D20" s="33" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="10">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Hedges of net investment in foreign operations [abstract]</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-    </row>
-    <row r="22" ht="23.85" customHeight="1" s="10">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="10">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Gains (losses) on hedges of net investments in foreign operations, net of tax</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="23.85" customHeight="1" s="10">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="32" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="10">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Reclassification adjustments on hedges of net investments in foreign operations, net of tax</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-    </row>
-    <row r="24" ht="23.85" customHeight="1" s="10">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="32" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="10">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>Other comprehensive income, net of tax, hedges of net investments in foreign operations</t>
         </is>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="29">
         <f>1*B22+1*B23</f>
         <v/>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="29">
         <f>1*C22+1*C23</f>
         <v/>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="10">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="D24" s="33" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="10">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Exchange differences on translation [abstract]</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-    </row>
-    <row r="26" ht="23.85" customHeight="1" s="10">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="10">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Gains (losses) on exchange differences on translation of foreign operations, net of tax</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-    </row>
-    <row r="27" ht="23.85" customHeight="1" s="10">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="32" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="10">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Reclassification adjustments on exchange differences on translation of foreign operations, net of tax</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-    </row>
-    <row r="28" ht="23.85" customHeight="1" s="10">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B27" s="27" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="32" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="10">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Other comprehensive income, net of tax, exchange differences on translation of foreign operations</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-    </row>
-    <row r="29" ht="23.85" customHeight="1" s="10">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="B28" s="27" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="32" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="10">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Financial assets measured at fair value through other comprehensive income [abstract]</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-    </row>
-    <row r="30" ht="23.85" customHeight="1" s="10">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="B29" s="25" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="10">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Gains (losses) on financial assets measured at fair value through other comprehensive income, net of tax</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-    </row>
-    <row r="31" ht="23.85" customHeight="1" s="10">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B30" s="27" t="n"/>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="32" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="10">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Reclassification adjustments on financial assets measured at fair value through other comprehensive income, net of tax</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-    </row>
-    <row r="32" ht="35.05" customHeight="1" s="10">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="B31" s="27" t="n"/>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="32" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="10">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Amounts removed from equity and adjusted against fair value of financial assets on reclassification out of fair value through other comprehensive income measurement category, net of tax</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-    </row>
-    <row r="33" ht="23.85" customHeight="1" s="10">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="B32" s="27" t="n"/>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="32" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="10">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Other comprehensive income, net of tax, financial assets measured at fair value through other comprehensive income</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="29">
         <f>1*B26+1*B27+1*B28+1*B30+1*B31+1*B32</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="29">
         <f>1*C26+1*C27+1*C28+1*C30+1*C31+1*C32</f>
         <v/>
       </c>
-    </row>
-    <row r="34" ht="35.05" customHeight="1" s="10">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="D33" s="33" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="10">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Share of other comprehensive income of associates and joint ventures accounted for using equity method that will be reclassified to profit or loss, net of tax</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-    </row>
-    <row r="35" ht="23.85" customHeight="1" s="10">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="B34" s="27" t="n"/>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="32" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="10">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>Others comprehensive income, net of tax, gains (losses) on other items</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-    </row>
-    <row r="36" ht="23.85" customHeight="1" s="10">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="32" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="10">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>Total other comprehensive income that will be reclassified to profit or loss, net of tax</t>
         </is>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="29">
         <f>1*B34+1*B35</f>
         <v/>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="29">
         <f>1*C34+1*C35</f>
         <v/>
       </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="10">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="D36" s="33" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="10">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>Total other comprehensive income</t>
         </is>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="29">
         <f>1*B11+1*B15+1*B36</f>
         <v/>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="29">
         <f>1*C11+1*C15+1*C36</f>
         <v/>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="10">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="D37" s="33" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="10">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>Total comprehensive income</t>
         </is>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="29">
         <f>1*B7+1*B37</f>
         <v/>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="29">
         <f>1*C7+1*C37</f>
         <v/>
       </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="10">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="D38" s="33" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="10">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>Comprehensive income attributable to [abstract]</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="10">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="25" t="n"/>
+      <c r="D39" s="31" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="10">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>Total comprehensive income, attributable to owners of parent</t>
         </is>
       </c>
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="18" t="n"/>
-    </row>
-    <row r="41" ht="23.85" customHeight="1" s="10">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="B40" s="29" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="33" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="10">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>Total comprehensive income, attributable to non-controlling interests</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="10">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="B41" s="29" t="n"/>
+      <c r="C41" s="29" t="n"/>
+      <c r="D41" s="33" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="10">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>Total comprehensive income</t>
         </is>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="29">
         <f>1*B40+1*B41</f>
         <v/>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="29">
         <f>1*C40+1*C41</f>
         <v/>
       </c>
+      <c r="D42" s="33" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
